--- a/ykk-dsr/hub/tc-out/[Sutrix] DSR -586- [レイアウト] 製品詳細 Overlay化（json2html）・項目fix版連携_TestData.xlsx
+++ b/ykk-dsr/hub/tc-out/[Sutrix] DSR -586- [レイアウト] 製品詳細 Overlay化（json2html）・項目fix版連携_TestData.xlsx
@@ -518,12 +518,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1.0, 3.0, 4.0, 5.0, 10.0, 12.0–19.0</t>
+          <t>1.0, 3.0, 4.0, 5.0, 10.0, 12.0–21.0</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Full product: CF commune + CF related, live</t>
+          <t>Full product (ver0.4): CF commune + CF related, live</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -533,12 +533,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>productId / productName / productCode / description / media01Asset / specs / publishDate · CF related: isActive / product</t>
+          <t>required: productId / productCode / productName / productCategories / applications / media01Asset / publishDate · display: description / itemVariations / colorVariations / colorVariationsPdf / notice / printableTape+Note / recycledTape+Note · new: itemVariationsImage / colorVariationsImage / howToUse / howToUseImage / recycledMaterial+Note · media02Type+Asset / media03Type+Url · CF related: isActive / product</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>990586001 / QA586 product A / QA586-A / 'QA586 description for SEO check' / any QA image / fill any 3 spec fields / 2026-10-01 · isActive ON / product = CF commune above</t>
+          <t>990586001 / QA586-A / QA586 product A / any / any / QA image 1 / 2026-10-01 · 'QA586 description for SEO check' / table 2×2 'QA586 item' / 'QA586 colors' / any QA PDF / 'QA586 notice' / ON+'QA586 print note' / ON+'QA586 recycled tape note' · QA images 2–4 / 'QA586 how to use' / QA image 5 / ON+'QA586 recycled material note' · Image + QA image 6 / External + https://www.ykkfastening.com/ · isActive ON / product = CF commune above</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>CF commune: Author → Assets → https://author-p192812-e2014374.adobeaemcloud.com/assets.html/content/dam/common/ja/products → Create → Content Fragment → model DM_product → Name = id (e.g. 990586001, digits only) → fill values from TestData sheet → Save → Manage Publication → Publish (live).</t>
+          <t>CF commune: Author → https://author-p192812-e2014374.adobeaemcloud.com/assets.html/content/dam/common/ja/products → Create → Content Fragment → model DM_product (ver0.4) → Name = productId (e.g. 990586001, digits only, no prefix) → fill the 7 required fields (productId, productCode, productName, productCategories, applications, media01Asset = image, publishDate) + the other TestData values → Save → Manage Publication → Publish (live). Other TDs: required fields only, values as TestData.</t>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Folder missing → note it, skip that TD</t>
+          <t>Folder missing → note it, skip that TD · required field not in model → note, continue</t>
         </is>
       </c>
     </row>
